--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1917,32 +1917,32 @@
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>weather.source</t>
+          <t>weather.source, weather.csv_path</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>synthetic</t>
+          <t>csv_typical_year (ενεργό) / synthetic (fallback)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>PLACEHOLDER (fallback, όχι πλέον default)</t>
+          <t>SOURCED (ενεργό) / PLACEHOLDER (fallback)</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Συνθετική γεννήτρια καιρού (sine waves), κρατιέται μόνο ως fallback source — δες τη γραμμή 'Πηγή καιρού (τυπικό έτος)' για την ενεργή πηγή</t>
+          <t>Ενεργή πηγή: csv_typical_year -- πραγματικά ιστορικά δεδομένα (θερμοκρασία/υγρασία/ηλιακή ακτινοβολία), 10ετία 2015-2024, Αλεξάνδρεια Ημαθίας, μέσος όρος ανά μήνα/ημέρα/ώρα σε 'τυπικό έτος' από Open-Meteo. Αποκάλυψε ένα πραγματικό bug στον αερισμό (βλ. γραμμή 'Κατώφλι σκίασης') που το συνθετικό μοντέλο έκρυβε -- μετά τη διόρθωση: yield 150 ημερών 14.11-&gt;32.79 kg/m2, min εσωτερική θερμοκρασία 3.9C-&gt;15.6C. Fallback: synthetic -- συνθετική γεννήτρια καιρού (sine waves), κρατιέται μόνο ως fallback source, όχι πλέον default.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>docs/assumptions/weather.md — υψηλότερης αξίας μελλοντική αναβάθμιση: αλλαγή σε 'csv'</t>
+          <t>docs/papers/open-meteo-historical-weather-api.md</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>config/greenhouse_example.yaml</t>
+          <t>twin/weather.py, scripts/fetch_weather.py, config/greenhouse_example.yaml</t>
         </is>
       </c>
     </row>
@@ -2652,143 +2652,143 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Πηγή καιρού (τυπικό έτος)</t>
+          <t>Ενεργοποίηση fan-pad ψύξης</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>weather.source=csv_typical_year, weather.csv_path</t>
+          <t>climate_control.fan_pad_cooling_enabled</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>10ετία 2015-2024, Αλεξάνδρεια Ημαθίας</t>
+          <t>true (ενεργό σε αυτό το config, default false)</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>SOURCED (ενεργό)</t>
+          <t>Επιλογή config</t>
         </is>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Πραγματικά ιστορικά δεδομένα (θερμοκρασία/υγρασία/ηλιακή ακτινοβολία) από Open-Meteo, μέσος όρος ανά μήνα/ημέρα/ώρα σε 'τυπικό έτος' — ενεργή πηγή καιρού (config/greenhouse_example.yaml). Αποκάλυψε ένα πραγματικό bug στον αερισμό (βλ. γραμμή 'Κατώφλι σκίασης') που το συνθετικό μοντέλο έκρυβε — μετά τη διόρθωση: yield 150 ημερών 14.11→32.79 kg/m², min εσωτερική θερμοκρασία 3.9°C→15.6°C.</t>
+          <t>Αρχική on/off επιλογή στο config για το αν το θερμοκήπιο διαθέτει σύστημα εξατμιστικής ψύξης fan-pad — ζητήθηκε ρητά από τον χρήστη. Ενεργοποιήθηκε στο ενεργό config μετά από δοκιμή 300 ημερών (1/3/2027, καλύπτει καλοκαίρι) που έδειξε μεγάλο όφελος: max εσωτερική θερμοκρασία 35.6°C→25.5°C, ώρες &gt;28°C 955→0, yield 76.67→92.26 kg/m². Default false στον κώδικα για νέα configs, καθώς δεν έχει επιβεβαιωθεί αν η πραγματική προσφορά (OptiClima cooling panels) αφορά fan-pad θερμοκρασιακή ψύξη ή μόνο αφύγρανση.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>papers/open-meteo-historical-weather-api.md</t>
+          <t>Επιλογή χρήστη, δεν υπάρχει βιβλιογραφική πηγή</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>twin/weather.py, scripts/fetch_weather.py</t>
+          <t>twin/params.py, twin/climate_model.py</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Ενεργοποίηση fan-pad ψύξης</t>
+          <t>Απόδοση fan-pad ψύξης</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>climate_control.fan_pad_cooling_enabled</t>
+          <t>climate_control.fan_pad_efficiency</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>true (ενεργό σε αυτό το config, default false)</t>
+          <t>0.80</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Επιλογή config</t>
+          <t>SOURCED</t>
         </is>
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Αρχική on/off επιλογή στο config για το αν το θερμοκήπιο διαθέτει σύστημα εξατμιστικής ψύξης fan-pad — ζητήθηκε ρητά από τον χρήστη. Ενεργοποιήθηκε στο ενεργό config μετά από δοκιμή 300 ημερών (1/3/2027, καλύπτει καλοκαίρι) που έδειξε μεγάλο όφελος: max εσωτερική θερμοκρασία 35.6°C→25.5°C, ώρες &gt;28°C 955→0, yield 76.67→92.26 kg/m². Default false στον κώδικα για νέα configs, καθώς δεν έχει επιβεβαιωθεί αν η πραγματική προσφορά (OptiClima cooling panels) αφορά fan-pad θερμοκρασιακή ψύξη ή μόνο αφύγρανση.</t>
+          <t>Κλάσμα απόστασης από ξηρή εξωτερική θερμοκρασία προς τον υγρό βολβό (wet-bulb) που φτάνει ο αέρας μετά τα pads — UF/IFAS 85% για καλά συντηρημένο σύστημα, Alabama Extension 70-85%. Χρησιμοποιείται μαζί με τύπο Stull (2011) για wet-bulb. Ενεργοποιεί ταυτόχρονα ψύξη ΚΑΙ αύξηση υγρασίας (αδιαβατική διεργασία) στον ενεργό αερισμό.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>Επιλογή χρήστη, δεν υπάρχει βιβλιογραφική πηγή</t>
+          <t>papers/fan-pad-evaporative-cooling.md</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>twin/params.py, twin/climate_model.py</t>
+          <t>twin/climate_model.py</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Απόδοση fan-pad ψύξης</t>
+          <t>Φωτοσύνθεση κόμης (self-shading)</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>climate_control.fan_pad_efficiency</t>
+          <t>_canopy_light_response (twin/crop_model.py)</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>k=0.75 (ίδιο με το υπάρχον)</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>SOURCED</t>
+          <t>SOURCED, bug fix</t>
         </is>
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Κλάσμα απόστασης από ξηρή εξωτερική θερμοκρασία προς τον υγρό βολβό (wet-bulb) που φτάνει ο αέρας μετά τα pads — UF/IFAS 85% για καλά συντηρημένο σύστημα, Alabama Extension 70-85%. Χρησιμοποιείται μαζί με τύπο Stull (2011) για wet-bulb. Ενεργοποιεί ταυτόχρονα ψύξη ΚΑΙ αύξηση υγρασίας (αδιαβατική διεργασία) στον ενεργό αερισμό.</t>
+          <t>Πριν: gross assimilation = ρυθμός ενός φύλλου στο πλήρες φως × LAI — σαν όλα τα φύλλα να έβλεπαν τον ίδιο ήλιο. Πραγματικά τα κατώτερα φύλλα σκιάζονται. Αυτό υπερεκτιμούσε δυσανάλογα περισσότερο το χαμηλό φως (χειμώνας) παρά το υψηλό (καλοκαίρι) — Νοέμβριος (89 W/m²) έδινε σχεδόν όσο ο Μάιος (262 W/m², 3x φως). Διορθώθηκε με ολοκλήρωμα Beer-Lambert/Michaelis-Menten (de Wit/Goudriaan τύπος). Yield 300 ημερών: 92.98→42.58 kg/m² (πιο ρεαλιστικό — κάτω από ολλανδικό όριο χωρίς τεχνητό φωτισμό, ενώ πριν ήταν στο επίπεδο ρεκόρ Ολλανδίας χωρίς καν να έχουμε τεχνητό φωτισμό).</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>papers/fan-pad-evaporative-cooling.md</t>
+          <t>papers/canopy-self-shading-photosynthesis.md</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>twin/climate_model.py</t>
+          <t>twin/crop_model.py</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Φωτοσύνθεση κόμης (self-shading)</t>
+          <t>Αναφορά αναπνοής (high-water mark)</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>_canopy_light_response (twin/crop_model.py)</t>
+          <t>CropState.respiration_reference_g_m2 (twin/crop_model.py)</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>k=0.75 (ίδιο με το υπάρχον)</t>
+          <t>-</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>SOURCED, bug fix</t>
+          <t>PLACEHOLDER, bug fix</t>
         </is>
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Πριν: gross assimilation = ρυθμός ενός φύλλου στο πλήρες φως × LAI — σαν όλα τα φύλλα να έβλεπαν τον ίδιο ήλιο. Πραγματικά τα κατώτερα φύλλα σκιάζονται. Αυτό υπερεκτιμούσε δυσανάλογα περισσότερο το χαμηλό φως (χειμώνας) παρά το υψηλό (καλοκαίρι) — Νοέμβριος (89 W/m²) έδινε σχεδόν όσο ο Μάιος (262 W/m², 3x φως). Διορθώθηκε με ολοκλήρωμα Beer-Lambert/Michaelis-Menten (de Wit/Goudriaan τύπος). Yield 300 ημερών: 92.98→42.58 kg/m² (πιο ρεαλιστικό — κάτω από ολλανδικό όριο χωρίς τεχνητό φωτισμό, ενώ πριν ήταν στο επίπεδο ρεκόρ Ολλανδίας χωρίς καν να έχουμε τεχνητό φωτισμό).</t>
+          <t>ΑΝΑΘΕΩΡΗΘΗΚΕ αυθημερόν: η πρώτη προσπάθεια (respiration_deficit_g_m2, "αποπλήρωσε πλήρως πριν καρπό") διόρθωσε το πρόσημο αλλά διπλομέτραγε την απώλεια -- ~480 απο ~1505 g/m2 συνολικής φωτοσύνθεσης (32%) εκτρεπόταν ΔΕΥΤΕΡΗ φορά, ενώ ήδη είχε αφαιρεθεί μία φορά από τη standing biomass. yield 150 ημερών έπεσε στα 6.21. Διορθώθηκε σωστά με respiration_reference_g_m2: τρέχον ιστορικό μέγιστο (high-water mark) της standing biomass -- η αναπνοή χρεώνεται σε αυτό, οχι στην τρέχουσα (συρρικνούμενη) τιμή, άρα μια κακή νύχτα κοστίζει ΜΙΑ φορά, όχι δύο. Αποτέλεσμα: yield 150 ημερών επέστρεψε στα 13.06 kg/m2 (κοντά στο 13.38 πριν τα δύο αυτά fixes), και το sweep νυχτερινού setpoint δείχνει σωστή κορυφή στους 16-17°C.</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>papers/canopy-self-shading-photosynthesis.md</t>
+          <t>docs/assumptions/crop-model.md</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
@@ -2800,72 +2800,35 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Αναφορά αναπνοής (high-water mark)</t>
+          <t>Ευαισθησία γονιμοποίησης στη θερμοκρασία</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>CropState.respiration_reference_g_m2 (twin/crop_model.py)</t>
+          <t>FRUIT_SET_T_MIN_C, FRUIT_SET_T_OPT_C, FRUIT_SET_T_MAX_C, _fruit_set_temp_response (twin/crop_model.py)</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>12.0 / 18.0 / 24.0 °C</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>PLACEHOLDER, bug fix</t>
+          <t>SOURCED, bug fix</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>ΑΝΑΘΕΩΡΗΘΗΚΕ αυθημερόν: η πρώτη προσπάθεια (respiration_deficit_g_m2, "αποπλήρωσε πλήρως πριν καρπό") διόρθωσε το πρόσημο αλλά διπλομέτραγε την απώλεια -- ~480 απο ~1505 g/m2 συνολικής φωτοσύνθεσης (32%) εκτρεπόταν ΔΕΥΤΕΡΗ φορά, ενώ ήδη είχε αφαιρεθεί μία φορά από τη standing biomass. yield 150 ημερών έπεσε στα 6.21. Διορθώθηκε σωστά με respiration_reference_g_m2: τρέχον ιστορικό μέγιστο (high-water mark) της standing biomass -- η αναπνοή χρεώνεται σε αυτό, οχι στην τρέχουσα (συρρικνούμενη) τιμή, άρα μια κακή νύχτα κοστίζει ΜΙΑ φορά, όχι δύο. Αποτέλεσμα: yield 150 ημερών επέστρεψε στα 13.06 kg/m2 (κοντά στο 13.38 πριν τα δύο αυτά fixes), και το sweep νυχτερινού setpoint δείχνει σωστή κορυφή στους 16-17°C.</t>
+          <t>Πραγματική βιβλιογραφία για ευαισθησία γονιμοποίησης (κάτω από 55°F ανθόπτωση, ιδανικό 60-70°F, πάνω από 75°F παρεμβολή γυρεοσωλήνα). Χρειάστηκε EMA θερμοκρασίας (12ωρο half-life) ώστε μια κρύα νύχτα να κουβαλάει ποινή στην επόμενη μέρα. Μετά τη διόρθωση του διπλομετρήματος αναπνοής (βλ. row 62), η κορυφή του sweep πλέον πέφτει στους 16-17°C -- πολύ κοντά στο βιβλιογραφικό 17-18°C, όχι πια στους 12°C.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>docs/assumptions/crop-model.md</t>
+          <t>papers/tomato-fruit-set-temperature-sensitivity.md</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
-        <is>
-          <t>twin/crop_model.py</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>Ευαισθησία γονιμοποίησης στη θερμοκρασία</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>FRUIT_SET_T_MIN_C, FRUIT_SET_T_OPT_C, FRUIT_SET_T_MAX_C, _fruit_set_temp_response (twin/crop_model.py)</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>12.0 / 18.0 / 24.0 °C</t>
-        </is>
-      </c>
-      <c r="D63" s="4" t="inlineStr">
-        <is>
-          <t>SOURCED, bug fix</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>Πραγματική βιβλιογραφία για ευαισθησία γονιμοποίησης (κάτω από 55°F ανθόπτωση, ιδανικό 60-70°F, πάνω από 75°F παρεμβολή γυρεοσωλήνα). Χρειάστηκε EMA θερμοκρασίας (12ωρο half-life) ώστε μια κρύα νύχτα να κουβαλάει ποινή στην επόμενη μέρα. Μετά τη διόρθωση του διπλομετρήματος αναπνοής (βλ. row 62), η κορυφή του sweep πλέον πέφτει στους 16-17°C -- πολύ κοντά στο βιβλιογραφικό 17-18°C, όχι πια στους 12°C.</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>papers/tomato-fruit-set-temperature-sensitivity.md</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr">
         <is>
           <t>twin/crop_model.py</t>
         </is>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2831,6 +2831,43 @@
       <c r="G62" s="2" t="inlineStr">
         <is>
           <t>twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Χωρητικότητα αφύγρανσης</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>climate_control.dehumidification_capacity_kg_water_per_hour</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>75.0 kg/ώρα</t>
+        </is>
+      </c>
+      <c r="D63" s="4" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER, bug fix</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>Πριν: η ενεργή αφύγρανση θεωρούνταν απεριόριστη (πάντα φτάνει το setpoint μέσα στην ώρα) -- ανοιχτό κενό γιατί η προσφορά δεν έχει spec χωρητικότητας για το OptiClima σύστημα. Τώρα υπάρχει πραγματικό όριο: ζήτηση πάνω από αυτό μένει ως αυξημένη υγρασία, δεν εξαφανίζεται. Τεκμηριωμένο σε συγκρίσιμα πραγματικά συστήματα (DryGair DG-12: 48kg/ώρα, semi-closed θερμοκήπιο: ~75kg/ώρα) -- όχι πραγματικό spec αυτού του μηχανήματος.</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>docs/papers/greenhouse-dehumidification-capacity.md</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/climate_model.py</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G63"/>
+  <dimension ref="A1:G64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2868,6 +2868,43 @@
       <c r="G63" s="2" t="inlineStr">
         <is>
           <t>twin/params.py, twin/climate_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Διάρκεια προσομοίωσης</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>simulation.duration_days</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>330 ημέρες (11 μήνες)</t>
+        </is>
+      </c>
+      <c r="D64" s="4" t="inlineStr">
+        <is>
+          <t>SOURCED, bug fix</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>Πριν: 150 ημέρες χωρίς καμία τεκμηρίωση/λογική (ο χρήστης ρώτησε απευθείας αν ήταν random -- ήταν). Η ντομάτα θερμοκηπίου είναι indeterminate, χωρίς φυσικό τέλος ζωής -- συνεχίζει να μεγαλώνει/καρποφορεί μέχρι ασθένεια, καταπόνηση, ή απόφαση τερματισμού. Πραγματικοί εμπορικοί κύκλοι καλλιέργειας διαρκούν ~10-11 μήνες πριν την επανφύτευση. 330 ημέρες = 11 μήνες. Το dataclass default στο twin/params.py (ήταν 120, ασυνεπές με το config) διορθώθηκε επίσης. Yield 330 ημερών (default config): 13.32 kg/m2.</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>docs/papers/tomato-crop-cycle-duration.md</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>config/greenhouse_example.yaml, twin/params.py</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -2847,7 +2847,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>75.0 kg/ώρα</t>
+          <t>771.0 kg/ώρα</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
@@ -2857,7 +2857,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Πριν: η ενεργή αφύγρανση θεωρούνταν απεριόριστη (πάντα φτάνει το setpoint μέσα στην ώρα) -- ανοιχτό κενό γιατί η προσφορά δεν έχει spec χωρητικότητας για το OptiClima σύστημα. Τώρα υπάρχει πραγματικό όριο: ζήτηση πάνω από αυτό μένει ως αυξημένη υγρασία, δεν εξαφανίζεται. Τεκμηριωμένο σε συγκρίσιμα πραγματικά συστήματα (DryGair DG-12: 48kg/ώρα, semi-closed θερμοκήπιο: ~75kg/ώρα) -- όχι πραγματικό spec αυτού του μηχανήματος.</t>
+          <t>ΑΝΑΘΕΩΡΗΘΗΚΕ αυθημερόν: το αρχικό 75 kg/ώρα (από φορητή μονάδα DryGair DG-12, καλύπτει ~3.700m²) ήταν αναντιστοιχία κλίμακας -- ο χρήστης παρατήρησε ότι το yield 330 ημερών (13.3 kg/m²) ήταν πολύ χαμηλότερο από τη δική του προσδοκία (30-50 kg/m² καλή σοδειά). Sensitivity sweep επιβεβαίωσε ότι αυτή η παράμετρος ήταν ο κυρίαρχος μοχλός. Η πραγματική προσφορά περιγράφει πλήρες "semi-closed greenhouse climate system" (OptiClima, €195.000), όχι φορητή μονάδα. Επαναβαθμονομήθηκε από ψυκτική ικανότητα semi-closed θερμοκηπίου (350 W/m², μεσαίο ενός εύρους 150-700) × 5000m² × ~30% latent fraction ≈ 771 kg/ώρα. Αποτέλεσμα: yield 330 ημερών 13.32→39.95 kg/m², μέσα στο αναμενόμενο εύρος του χρήστη.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -2894,7 +2894,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Πριν: 150 ημέρες χωρίς καμία τεκμηρίωση/λογική (ο χρήστης ρώτησε απευθείας αν ήταν random -- ήταν). Η ντομάτα θερμοκηπίου είναι indeterminate, χωρίς φυσικό τέλος ζωής -- συνεχίζει να μεγαλώνει/καρποφορεί μέχρι ασθένεια, καταπόνηση, ή απόφαση τερματισμού. Πραγματικοί εμπορικοί κύκλοι καλλιέργειας διαρκούν ~10-11 μήνες πριν την επανφύτευση. 330 ημέρες = 11 μήνες. Το dataclass default στο twin/params.py (ήταν 120, ασυνεπές με το config) διορθώθηκε επίσης. Yield 330 ημερών (default config): 13.32 kg/m2.</t>
+          <t>Πριν: 150 ημέρες χωρίς καμία τεκμηρίωση/λογική (ο χρήστης ρώτησε απευθείας αν ήταν random -- ήταν). Η ντομάτα θερμοκηπίου είναι indeterminate, χωρίς φυσικό τέλος ζωής -- συνεχίζει να μεγαλώνει/καρποφορεί μέχρι ασθένεια, καταπόνηση, ή απόφαση τερματισμού. Πραγματικοί εμπορικοί κύκλοι καλλιέργειας διαρκούν ~10-11 μήνες πριν την επανφύτευση. 330 ημέρες = 11 μήνες. Το dataclass default στο twin/params.py (ήταν 120, ασυνεπές με το config) διορθώθηκε επίσης. Yield 330 ημερών (default config): 13.32 kg/m2 (πριν την αναθεώρηση της χωρητικότητας αφύγρανσης στα 771 kg/ώρα -- βλ. row 63 -- yield 330 ημερών τώρα 39.95 kg/m2).</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G66"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2905,6 +2905,80 @@
       <c r="G64" s="2" t="inlineStr">
         <is>
           <t>config/greenhouse_example.yaml, twin/params.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Ειδική ηλεκτρική κατανάλωση αφύγρανσης</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>climate_control.dehumidification_specific_power_kwh_per_kg</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>0.22 kWh/kg</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>Ηλεκτρική ενέργεια ανά kg νερού που πραγματικά αφαιρείται από την ενεργή αφύγρανση. Πρώτη φάση οικονομικής ανάλυσης (2026-08-25): ο χρήστης διευκρίνισε ότι το ρεύμα του CHP πωλείται στο δίκτυο (δεν καλύπτει την κατανάλωση του θερμοκηπίου) -- το θερμοκήπιο αγοράζει 100% από το δίκτυο. Τιμή από το ίδιο DryGair DG-12 (9.55 kW / ~45 kg/ώρα ≈ 4.5 kg/kWh ≈ 0.22 kWh/kg) που είχε ήδη απορριφθεί για τη χωρητικότητά του (κλίμακα), αλλά η ενεργειακή απόδοση είναι ιδιότητα της τεχνολογίας ψυκτικού κύκλου, όχι του μεγέθους της μονάδας -- μεταφέρεται ανεξάρτητα.</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>docs/papers/greenhouse-electricity-consumption.md</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/simulate.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Ειδική ηλεκτρική ισχύς ανεμιστήρων αερισμού</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>climate_control.ventilation_specific_fan_power_w_per_m3h</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>0.03 W/(m³/h)</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>Ηλεκτρική ισχύς ανά μονάδα ενεργού (πάνω από baseline) παροχής αέρα αερισμού, τιμολογείται μόνο όσες ώρες είναι ενεργό το fan-pad (climate_result.fan_pad_active) -- τα roof vents της πραγματικής προσφοράς είναι μηχανοκίνητα αλλά παθητικά (φυσικός αερισμός), όχι forced-air, άρα το baseline leakage δεν τιμολογείται. Μεσαία τιμή ενός εύρους 0.025-0.045 W/(m³/h) από πραγματικές μετρήσεις ανεμιστήρων θερμοκηπίου (παλαιότερα vs. νεότερα ενεργειακά αποδοτικά μοντέλα).</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>docs/papers/greenhouse-electricity-consumption.md</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/simulate.py, api/main.py</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G66"/>
+  <dimension ref="A1:G67"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -2977,6 +2977,43 @@
         </is>
       </c>
       <c r="G66" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/simulate.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Ισχύς ανεμιστήρων ανακυκλοφορίας (HAF)</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>climate_control.recirculation_fan_power_kw</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>4.7 kW</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>Συνολική ηλεκτρική ισχύς του HAF fan bank (ACF21 της προσφοράς, 508mm/5.400 m³/h έκαστος). Ο χρήστης μοιράστηκε το διάγραμμα διάταξης της προσφοράς (racetrack pattern) -- τα σύμβολα διακοπής '≶' δείχνουν ότι το μοτίβο επαναλαμβάνεται (δεν είναι κυριολεκτική καταμέτρηση). Εκτιμήθηκε από πραγματική γεωμετρία (5 bays x 100m) + κανόνα απόστασης HAF (~1 ανεμιστήρας κάθε 40-50 ft) = ~7/σειρά x 5 σειρές = 35 ανεμιστήρες x 5.400 m³/h x ~0.025 W/(m³/h) ειδική ισχύς ≈ 4.7 kW. Λειτουργούν όταν ο αερισμός είναι στο παθητικό baseline (ach&lt;=vent_min_ach), σβήνουν όταν ο αερισμός ενεργοποιείται ενεργά (πραγματική πρακτική HAF).</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>docs/papers/greenhouse-electricity-consumption.md</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
         <is>
           <t>twin/params.py, twin/simulate.py, api/main.py</t>
         </is>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G67"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3016,6 +3016,43 @@
       <c r="G67" t="inlineStr">
         <is>
           <t>twin/params.py, twin/simulate.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Ποικιλία τομάτας</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>crop.variety</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Beef τομάτα (EYRE RZ F1-class, ~230-280g)</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER, researched</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>Ξαναποφασίστηκε (ήταν καθαρό cosmetic placeholder 'Beefsteak tomato') μέσα από 3 άξονες: (1) αγρονομική καταλληλότητα Β. Ελλάδας -- AMATI F1 (semideterminate, συγκρούεται με τον συνεχή 330ήμερο κύκλο μας) και BELLADONA F1 (indeterminate αλλά ρητά ακατάλληλη για φθινοπωρινή/χειμερινή φύτευση, συγκρούεται με το Σεπτεμβριάτικο ξεκίνημα του config μας) απορρίφθηκαν· (2) ζήτηση αγοράς -- beef (~1€/kg, 65-70 kg/m²/έτος) vs cherry (~3€/kg, 20-40 kg/m²/έτος) βγαίνουν κοντά σε ακαθάριστο έσοδο/m² μετά τον υπολογισμό εργατικού κόστους -- beef επιλέχθηκε ως το καλύτερο καθαρό ταίριασμα, ήδη συμβατό με την υπάρχουσα πυκνότητα single-stem high-wire· (3) μεταποίηση -- ξεχωριστή αλυσίδα (υπαίθρια, όχι θερμοκηπιακή υδροπονία), καμία ρεαλιστική σύνδεση προστιθέμενης αξίας. Τελικά διασταυρώθηκε με πραγματικό precedent Β. Ελλάδας (Θερμοκήπια Σαββίδη/Dramello Fresh, CHP+υδροπονία, 250-280g beef) και ταιριάχτηκε με πραγματική, διαθέσιμη στην Ελλάδα ποικιλία στην ίδια κλάση μεγέθους (EYRE RZ F1, Rijk Zwaan). Ακόμα μόνο label -- καμία παράμετρος του crop model δεν συνδέεται ακόμα με την ποικιλία (σχεδιασμένο επόμενο βήμα: target βάρος καρπού, ρυθμός ταξιανθιών, ανοχή θερμοκρασίας fruit-set ως ρυθμιζόμενες παράμετροι sourced σε αυτή την κλάση).</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>docs/papers/tomato-variety-selection-northern-greece.md</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>config/greenhouse_example.yaml</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3053,6 +3053,154 @@
       <c r="G68" t="inlineStr">
         <is>
           <t>config/greenhouse_example.yaml</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Target βάρος καρπού</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>crop.target_fruit_weight_g</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>255.0 g</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>Μεσαία τιμή του εύρους 230-280g της EYRE RZ F1 (Rijk Zwaan, η επιλεγμένη κλάση ποικιλίας). Δεν τροφοδοτεί ακόμα τη φυσική του crop model (η ανάπτυξη καρπού παραμένει συνεχής, βασισμένη σε fruit_partition_fraction_max) -- χρησιμοποιείται σαν σταθερά μετατροπής της σωρευτικής παραγωγής σε trusses/εβδομάδα, ώστε ένας καλλιεργητής να μπορεί να το ελέγξει με πραγματικά νούμερα.</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>docs/papers/tomato-variety-selection-northern-greece.md</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Καρποί ανά τσαμπί</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>crop.fruits_per_truss</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>5.0</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>SOURCED (class-level)</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>Γενική τιμή αναφοράς για beef/TOV-τύπου indeterminate θερμοκηπιακή τομάτα (4-6 καρποί/τσαμπί σε πολλαπλές πηγές) -- όχι επίσημο spec της EYRE RZ F1 (δεν είναι δημόσια διαθέσιμο). Χρησιμοποιείται μαζί με το target_fruit_weight_g για τον υπολογισμό του ρυθμού ταξιανθιών.</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>docs/papers/tomato-variety-selection-northern-greece.md</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Fruit Set % (έξοδος)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>summary.avg_fruit_set_pct, daily_series.fruit_set_pct</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Derived output</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>Εκθέτει τον ήδη υπάρχοντα εσωτερικό συντελεστή _fruit_set_temp_response (0-1, θερμοκρασιακή απόκριση γονιμοποίησης) ως πραγματικό ποσοστό. Καμία νέα φυσική -- surfacing υπάρχοντος υπολογισμού. Cross-check 2026-08-26: ρεαλιστικό μοτίβο (90-100% φθινόπωρο/χειμώνα/άνοιξη, πτώση σε 50-65% το καλοκαίρι λόγω θερμικού στρες).</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>docs/assumptions/crop-model.md</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>twin/crop_model.py, twin/simulate.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Ρυθμός ταξιανθιών (έξοδος)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>summary.final_trusses_per_plant, summary.avg_truss_rate_per_week</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>Derived output</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>Παράγεται διαιρώντας τη σωρευτική παραγωγή (final_yield_kg_m2) με (πυκνότητα x target_fruit_weight_g x fruits_per_truss) -- μετατροπή αναφοράς, όχι νέα φυσική διακριτής μέτρησης ταξιανθιών. Cross-check 2026-08-26: το 330ήμερο default config βγάζει ~0.27 τσαμπιά/εβδομάδα, πολύ χαμηλότερο από το πραγματικό εμπορικό benchmark (~1/εβδομάδα) -- ίδιο, ήδη τεκμηριωμένο yield gap (39.95 vs 65-70 kg/m²/έτος), όχι νέο πρόβλημα.</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>docs/assumptions/crop-model.md</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>api/main.py</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>summary.final_trusses_per_plant, summary.avg_truss_rate_per_week</t>
+          <t>summary.final_trusses_per_stem, summary.avg_truss_rate_per_week</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -3190,7 +3190,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Παράγεται διαιρώντας τη σωρευτική παραγωγή (final_yield_kg_m2) με (πυκνότητα x target_fruit_weight_g x fruits_per_truss) -- μετατροπή αναφοράς, όχι νέα φυσική διακριτής μέτρησης ταξιανθιών. Cross-check 2026-08-26: το 330ήμερο default config βγάζει ~0.27 τσαμπιά/εβδομάδα, πολύ χαμηλότερο από το πραγματικό εμπορικό benchmark (~1/εβδομάδα) -- ίδιο, ήδη τεκμηριωμένο yield gap (39.95 vs 65-70 kg/m²/έτος), όχι νέο πρόβλημα.</t>
+          <t>Παράγεται διαιρώντας τη σωρευτική παραγωγή (final_yield_kg_m2) με (πυκνότητα x stems_per_plant x target_fruit_weight_g x fruits_per_truss) -- μετατροπή αναφοράς, όχι νέα φυσική διακριτής μέτρησης ταξιανθιών. Cross-check 2026-08-26: το 330ήμερο default config βγάζει ~0.27 τσαμπιά/εβδομάδα, πολύ χαμηλότερο από το πραγματικό εμπορικό benchmark (~1/εβδομάδα) -- ίδιο, ήδη τεκμηριωμένο yield gap (39.95 vs 65-70 kg/m²/έτος), όχι νέο πρόβλημα.</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -3201,6 +3201,191 @@
       <c r="G72" t="inlineStr">
         <is>
           <t>api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Στελέχη ανά φυτό</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>crop.stems_per_plant</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>SITE-SPECIFIC</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>1 = single-stem (η βάση για τις πυκνότητες density_plants_per_m2/reference_density_plants_per_m2 αυτού του project), 2 = two-stem (ελέγχθηκε κατά την επιλογή ποικιλίας -- Belladona F1). Το μόνο πεδίο ποικιλίας που πραγματικά αλλάζει συμπεριφορά μοντέλου: το twin/crop_model.py _lai() κλιμακώνει την πυκνότητα κόμης με density_plants_per_m2 x stems_per_plant, και ο υπολογισμός ρυθμού ταξιανθιών στο api/main.py διαιρεί με την ίδια ενεργή πυκνότητα στελεχών (trusses ανά στέλεχος, όπως το μετράει πραγματικά ένας καλλιεργητής).</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Εσωτερική λογική μοντέλου</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/crop_model.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Θερμοκρασιακά όρια φωτοσύνθεσης</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>crop.photosynthesis_t_min_c / _t_opt_c / _t_max_c</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>10.0 / 27.0 / 35.0</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>Μετακινήθηκαν 2026-08-26 από σταθερές module (T_MIN_C/T_OPT_C/T_MAX_C) του twin/crop_model.py σε πεδία CropParams, ώστε η θερμοκρασιακή ανοχή μιας ποικιλίας να είναι ρύθμιση config, όχι αλλαγή κώδικα. Ίδιες τιμές, καμία αλλαγή συμπεριφοράς στο default της EYRE RZ F1-class.</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Frontiers 10.3389/fpls.2017.00365; researchgate 323225604</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Θερμοκρασιακά όρια fruit set</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>crop.fruit_set_t_min_c / _t_opt_c / _t_max_c</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>12.0 / 18.0 / 24.0</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>Μετακινήθηκαν 2026-08-26 από σταθερές module (FRUIT_SET_T_MIN/OPT/MAX_C). Πολύ πιο στενή ανοχή από τη φωτοσύνθεση -- και το χαρακτηριστικό που πραγματικά διαφέρει σημαντικά μεταξύ πραγματικών ποικιλιών (π.χ. Merlice F1 "very good fruit set at high temperatures" vs. αυτό το EYRE RZ F1-class default).</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>docs/papers/tomato-fruit-set-temperature-sensitivity.md</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Συντελεστής εξασθένησης φωτός κόμης</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>crop.canopy_light_extinction_coeff</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>Μετακινήθηκε 2026-08-26 από σταθερά module (CANOPY_LIGHT_EXTINCTION_COEFF). Beer-Lambert συντελεστής (0.7-0.9 εύρος για high-wire κόμες τομάτας), διαφέρει κάπως ανάλογα με τη φυλλική συνήθεια μιας ποικιλίας.</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>docs/papers/tomato-canopy-extinction-coefficient.md</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Κλάσμα συντήρησης αναπνοής/ημέρα</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>crop.maintenance_respiration_fraction_per_day</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>0.015</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>Μετακινήθηκε 2026-08-26 από σταθερά module (MAINTENANCE_RESPIRATION_FRACTION_PER_DAY), όχι ξεχωριστά τεκμηριωμένο. Η ζωτικότητα (και το φορτίο αναπνοής) ενός φυτού διαφέρει κάπως ανάλογα με την ποικιλία.</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/crop_model.py</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3386,6 +3386,43 @@
       <c r="G77" t="inlineStr">
         <is>
           <t>twin/params.py, twin/crop_model.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Ρυθμός ταξιανθιών (σταθερή φάση, έξοδος)</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>summary.steady_state_truss_rate_per_week, summary.full_production_start_day</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Derived output</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>Ίδιος υπολογισμός με το avg_truss_rate_per_week, αλλά μόνο πάνω στις μέρες μετά το full_production_start_day (fruiting_start_days + fruiting_ramp_days) -- εξαιρεί το παράθυρο εκκίνησης/βλαστικής φάσης (~55 μέρες, σχεδόν μηδενική παραγωγή) που αραίωνε τεχνητά τον μέσο όρο όλης της περιόδου. null όταν το duration_days δεν φτάνει το full_production_start_day. 330ήμερο default config: ~0.31/εβδ (steady-state) vs ~0.27/εβδ (όλη η περίοδος). Cross-check 2026-08-26: το αρχικό "~1/εβδ" benchmark που χρησιμοποιούσαμε ήταν λάθος-παραπεμπόμενο -- βλ. tomato-truss-rate-benchmark.md για το διορθωμένο, αυτοσυνεπές benchmark (~0.4-0.5/εβδ για μεγαλόκαρπη beef τομάτα).</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>docs/papers/tomato-truss-rate-benchmark.md</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>api/main.py</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3423,6 +3423,265 @@
       <c r="G78" t="inlineStr">
         <is>
           <t>api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Σύστημα υδροπονίας</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>hydroponic.system_type, hydroponic.substrate_type</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>"drip_substrate", "rockwool"</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>SOURCED (διόρθωση 2026-08-26, ήταν "NFT")</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>Το NFT ειναι για φυλλώδη λαχανικά, όχι indeterminate high-wire τομάτα. Πραγματικά παραδείγματα (Θερμοκήπια Σαββίδη/Dramello Fresh) και η προσφορά αυτού του project (Spagnol BravoJet EC/pH fertigation) δείχνουν υπόστρωμα (rockwool/coco) με σταξοάρδευση.</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>docs/assumptions/hydroponics.md, docs/papers/tomato-variety-selection-northern-greece.md, docs/papers/geothermiki-s192g-quote.md</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>twin/params.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>EC θρεπτικού διαλύματος (στόχος)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>hydroponic.ec_target_ms_cm</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>3.0 mS/cm</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>Συνήθως αναφερόμενο εύρος 2.0-3.5 mS/cm για θερμοκηπιακή τομάτα. Πλέον πραγματικό πεδίο CropParams που τροφοδοτεί τον υπολογισμό δοσομέτρησης λιπάσματος (Level A) -- πριν ήταν μόνο πληροφοριακό κείμενο στο tab "Συνταγή γεωπονίας".</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>docs/papers/hydroponic-fertigation-level-a.md</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/simulate.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>pH θρεπτικού διαλύματος (στόχος)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>hydroponic.ph_target</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>6.0</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>Συνήθως αναφερόμενο βέλτιστο εύρος διαθεσιμότητας θρεπτικών 5.5-6.5. Δεν τροφοδοτεί ακόμα καμία φυσική/απόδοση (Level B/C, μελλοντικό) -- μόνο εκτίθεται σαν config πεδίο.</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>docs/papers/hydroponic-fertigation-level-a.md</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>twin/params.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Στόχος drainage (leaching fraction)</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>hydroponic.drainage_target_fraction</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>0.25 (25%)</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>Συνήθως αναφερόμενο εύρος 20-30% για καλλιέργεια σε υπόστρωμα -- ξεπλένει συσσωρευμένα άλατα. Καθορίζει άμεσα τον όγκο άρδευσης: irrigation = διαπνοή / (1 - drainage_fraction).</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>docs/papers/hydroponic-fertigation-level-a.md</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/simulate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Ειδική ισχύς αντλίας άρδευσης</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>hydroponic.irrigation_pump_specific_power_kwh_per_m3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>0.28 kWh/m³</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>SOURCED (γενικός μέσος όρος, όχι spec συγκεκριμένης αντλίας)</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>Παγκόσμια μελέτη βρίσκει μέση ενεργειακή ένταση στάγδην άρδευσης ~1.0 MJ/m³ (=0.278 kWh/m³), χαμηλότερη από καταιονισμό (1.8 MJ/m³) λόγω χαμηλότερης πίεσης λειτουργίας. Δεν είναι spec της πραγματικής αντλίας BravoJet (δεν υπάρχει διαθέσιμο).</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Nature Communications (docs/papers/hydroponic-fertigation-level-a.md)</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/simulate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Συντελεστής μετατροπής EC-&gt;λίπασμα</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>hydroponic.fertilizer_g_per_l_per_ec_unit</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>0.64 g/L ανά μονάδα EC</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>Γενικός εμπειρικός συντελεστής μετατροπής EC-&gt;TDS (δεν υπάρχει καθολικός κανόνας -- εξαρτάται από το συγκεκριμένο μείγμα λιπάσματος, δεν έχουμε spec του πραγματικού προϊόντος). Το παραγόμενο total_fertilizer_dosed_kg να διαβάζεται σαν τάξη μεγέθους, όχι ακριβής μάζα.</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>docs/papers/hydroponic-fertigation-level-a.md</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/simulate.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Άρδευση/στράγγιση/λίπασμα/ηλεκτρικό fertigation (έξοδοι)</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>summary.total_irrigation_water_m3, summary.total_drainage_water_m3, summary.total_fertilizer_dosed_kg, summary.total_fertigation_elec_kwh, daily_series.irrigation_water_l_day, daily_series.drainage_water_l_day, daily_series.fertilizer_dosed_g_day, daily_series.fertigation_elec_kw</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Derived output</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Παράγονται από τη διαπνοή που ήδη υπολογίζει το crop model (όχι νέα φυσική) -- reporting/derivation layer, ίδιο μοτίβο με τα ηλεκτρικά αφύγρανσης/αερισμού/ανακυκλοφορίας. Η άρδευση είναι καθαρά demand-following (μηδέν τη νύχτα, καθώς η διαπνοή είναι μηδέν χωρίς φως) -- καμία διατήρηση/βασική άρδευση υποστρώματος δεν μοντελοποιείται.</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>docs/assumptions/hydroponics.md</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>twin/simulate.py, api/main.py</t>
         </is>
       </c>
     </row>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Οδηγός" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$93</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G85"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Συνήθως αναφερόμενο βέλτιστο εύρος διαθεσιμότητας θρεπτικών 5.5-6.5. Δεν τροφοδοτεί ακόμα καμία φυσική/απόδοση (Level B/C, μελλοντικό) -- μόνο εκτίθεται σαν config πεδίο.</t>
+          <t>Συνήθως αναφερόμενο βέλτιστο εύρος διαθεσιμότητας θρεπτικών 5.5-6.5. Τροφοδοτεί πλέον πραγματικά το marketable yield (Level B, 2026-08-29) μέσω συνεχούς παραβολικής καμπάνας γύρω από το βέλτιστο σημείο pH=5.5 -- δες γραμμές παρακάτω.</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3685,8 +3685,304 @@
         </is>
       </c>
     </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>EC βέλτιστο σημείο (peak yield)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>hydroponic.ec_optimal_ms_cm</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3.0 mS/cm</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Μελέτη σε θερμοκηπιακή τομάτα βρήκε μέγιστο yield στα 3 dS/m -- ανεβαίνει συνεχώς μέχρι εκεί, πέφτει συνεχώς μετά. Αντικατέστησε (2026-08-29) μια αρχική flat-plateau υλοποίηση (μηδενική διαφορά σε όλο το εμπορικό εύρος 2.0-3.5 mS/cm) που ο χρήστης εντόπισε ως λανθασμένη -- η πραγματική βιβλιογραφική καμπύλη έχει ένα και μοναδικό peak, όχι flat top.</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>ResearchGate — The Effect of EC Levels of Nutrient Solution on the Growth, Yield, and Quality of Tomatoes (docs/assumptions/hydroponics.md)</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>EC καμπυλότητα/όρια απώλειας (BER πάνω, έλλειψη κάτω)</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>hydroponic.ec_high_side_curvature_per_ms_cm2, ec_low_side_curvature_per_ms_cm2, ber_yield_loss_fraction_max, ec_deficiency_yield_loss_fraction_max</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>0.0444, 0.0375, 0.35 (35%), 0.50 (50%)</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (μηχανισμός SOURCED, μέγεθος εκτίμηση)</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>Συνεχής παραβολική απώλεια yield γύρω από το EC βέλτιστο σημείο -- κίνδυνος BER (Blossom End Rot, αλατότητα) πάνω από το peak, έλλειψη θρεπτικών κάτω από αυτό. Η καμπυλότητα επιλέχθηκε ώστε να διατηρεί περίπου το ίδιο μέγεθος απώλειας με μια προηγούμενη threshold-based υλοποίηση σε σημεία αναφοράς (π.χ. 10% απώλεια στα 4.5 mS/cm).</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>PMC — Saline Water Drip Irrigation BER Incidence, γενική καθοδήγηση καλλιεργητών (docs/assumptions/hydroponics.md)</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>pH βέλτιστο σημείο (peak yield)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>hydroponic.ph_optimal</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>5.5</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Πείραμα με pH 4.5/5.0/5.5/6.0/6.5 βρήκε μέγιστο yield ακριβώς στο 5.5. Αντικατέστησε (2026-08-29) μια αρχική flat-plateau υλοποίηση (5.5-6.5, μηδενική διαφορά σε όλο το εύρος) που ο χρήστης εντόπισε ως λανθασμένη -- ίδιο πρόβλημα με το EC παραπάνω.</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>ResearchGate — The Influence of pH of Nutrient Solution On Yield and Nutritional Status of Tomato Plants (docs/assumptions/hydroponics.md)</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>pH καμπυλότητα/cap διαθεσιμότητας θρεπτικών</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>hydroponic.ph_curvature_per_ph_unit2, ph_availability_penalty_cap_fraction</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>0.0667, 0.15 (15%)</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER (μηχανισμός SOURCED, μέγεθος εκτίμηση)</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>Συνεχής παραβολική απώλεια γύρω από το pH βέλτιστο σημείο -- κανένα ποσοτικοποιημένο ποσοστό δεν βρέθηκε στη βιβλιογραφία. Το cap είναι υψηλότερο από κάθε μεμονωμένο θρεπτικό στο damped tier παρακάτω, γιατί το pH γκαρδάρει τη διαθεσιμότητα όλων των θρεπτικών ταυτόχρονα, όχι μόνο ενός.</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>docs/assumptions/hydroponics.md</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>N/K/Mg/B στόχοι + εύρη επάρκειας (damped tier)</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>hydroponic.n_ppm/n_min_optimal_ppm/n_max_optimal_ppm, k_*, mg_*, b_*</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>N=105 (60-150), K=300 (199-400), Mg=65 (45-70), B=0.40 (0.30-0.50) ppm</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>SOURCED εύρη, PLACEHOLDER μηχανισμός ποινής</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>Εύρη από CEAC Arizona / Florida IFAS συνταγές θερμοκηπιακής τομάτας (Mg επιβεβαιώθηκε 2026-08-28 με άμεσο recheck του CEAC PDF). Πραγματικός αλλά σκόπιμα περιορισμένος (capped) μηχανισμός -- εντός εύρους καμία επίδραση στο marketable yield, εκτός γραμμική ποινή έως το ατομικό cap (βλ. επόμενη γραμμή).</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>CEAC Arizona tomato formula PDF, Florida EDIS HS796/CV216 (docs/assumptions/hydroponics.md)</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Cap ποινής/floor damped tier</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>hydroponic.damped_nutrient_penalty_cap_fraction, recipe_adequacy_multiplier_min</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>0.02 (2% ανά θρεπτικό), 0.85 (85% floor)</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>PLACEHOLDER</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Κάθε θρεπτικό (N/K/Mg/B) capped στο 2% ατομική ποινή όταν είναι ένα πλήρες εύρος-πλάτος εκτός επάρκειας· ο συνδυασμένος πολλαπλασιαστής των τεσσάρων clamped στο 0.85 ώστε το tier να μην μπορεί ποτέ να δώσει δυσανάλογα μεγάλη μεταβολή στο yield.</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>docs/assumptions/hydroponics.md</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>twin/params.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>P/S/Fe/Mn/Zn/Cu/Mo (πληροφοριακό tier)</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>hydroponic.p_ppm, s_ppm, fe_ppm, mn_ppm, zn_ppm, cu_ppm, mo_ppm</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>P=62, S=110, Fe=2.5, Mn=0.55, Zn=0.33, Cu=0.05, Mo=0.05 ppm</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>CEAC Arizona συνταγή -- μόνο εμφάνιση στο tab «Συνταγή γεωπονίας», καμία επίδραση στη φυσική (ίδια μεταχείριση με το block επικονίασης). Σημαντική απόκλιση πηγών στο Mn/Zn έναντι Florida IFAS (Zn: 0.33 vs 0.09 ppm, 3.6x διαφορά) -- τεκμηριωμένη, όχι επιλυμένη.</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>CEAC Arizona tomato formula PDF (docs/assumptions/hydroponics.md)</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>twin/params.py</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Marketable yield (Level B, έξοδοι)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>summary.ec_adjusted_final_yield_kg_m2, ber_yield_loss_fraction, ec_deficiency_yield_loss_fraction, ph_availability_multiplier, recipe_adequacy_multiplier, marketable_yield_kg_m2, total_marketable_yield_kg, daily_series.marketable_yield_kg_m2</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Derived output</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Το marketable yield (μετά EC/pH/θρεπτικά) υπολογίζεται σαν σταθερός πολλαπλασιαστικός παράγοντας πάνω στο ακατέργαστο yield του crop model -- ίδιο μοτίβο reporting-layer με το Level A. Το ίδιο ratio εφαρμόζεται σε κάθε ημέρα του daily_series (2026-08-29, διόρθωση) ώστε όλες οι απεικονίσεις yield στην εφαρμογή (header, tabs, σχηματικό) να είναι συνεπείς με το marketable yield, όχι μόνο το tab «Συνταγή γεωπονίας».</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>docs/assumptions/hydroponics.md</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>twin/params.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G55"/>
+  <autoFilter ref="A1:G93"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/docs/sources.xlsx
+++ b/docs/sources.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Οδηγός" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Παραδοχές'!$A$1:$G$94</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G93"/>
+  <dimension ref="A1:G94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -3981,8 +3981,45 @@
         </is>
       </c>
     </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Phase-aware θέρμανση (delta ανά φάση)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>climate_control.ramp_up_heating_setpoint_day_delta_c, ramp_up_heating_setpoint_night_delta_c, full_fruiting_heating_setpoint_day_delta_c, full_fruiting_heating_setpoint_night_delta_c</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>2.0, 2.0, 2.0, 2.0 °C</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>SOURCED</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Πρώτο πέρασμα phase-aware κλίματος (2026-08-31, μόνο θερμοκρασία -- CO2/αφύγρανση μελλοντικά, ίδιο μοτίβο). Φάση προκύπτει από τα ήδη υπάρχοντα crop.fruiting_start_days/fruiting_ramp_days (ίδιο boundary με το fruit-partition ramp), όχι νέο ξεχωριστό χρονοδιάγραμμα. heating_setpoint_day_c/night_c είναι πλέον ρητά το βλαστικό baseline· κάθε επόμενη φάση = baseline + delta. Γενική βιβλιογραφική καθοδήγηση αναφέρει επανειλημμένα ότι η περίοδος ανθοφορίας/καρποφορίας θέλει ~2°C θερμότερο target (ημέρα και νύχτα) από τη βλαστική φάση. Το ramp_up παίρνει το ίδιο delta με το full_fruiting (η πηγή δεν ξεχωρίζει ενδιάμεσο στόχο). Discrete step ακριβώς στο boundary, καμία ομαλή μετάβαση.</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Γενική βιβλιογραφία θερμοκηπιακής τομάτας (docs/assumptions/climate-control.md, docs/plans/2026-08-31-phase-aware-climate-design.md)</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>twin/params.py, twin/climate_model.py, twin/simulate.py, api/main.py</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:G93"/>
+  <autoFilter ref="A1:G94"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
